--- a/mygui_docking/Project1/x64/Release/sensor_data_2.xlsx
+++ b/mygui_docking/Project1/x64/Release/sensor_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxnkilmt\Documents\GitHub\ZJU_Oil\mygui_docking\Project1\x64\Release\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912A2E30-38CE-4A13-922E-71EDE894CEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B1FDB0-70D1-4F50-97D4-9FD807EDD68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
